--- a/outputs/496-15.xlsx
+++ b/outputs/496-15.xlsx
@@ -160,20 +160,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -369,389 +373,389 @@
   <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="n">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>44243</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>90108</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>-378.95</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="n">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>44243</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>90121</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>-500</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="n">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>44237</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>-347.51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="n">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>44230</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>155.86</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1" t="n">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>44237</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>-810.86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="n">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>44243</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>80095</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>-1900</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1" t="n">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>44239</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="4" t="n">
         <v>724.98</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="1" t="n">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>44237</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="4" t="n">
         <v>141.61</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="1" t="n">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>44235</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="4" t="n">
         <v>153.71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="1" t="n">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>80086</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="4" t="n">
         <v>-160</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1" t="n">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>44239</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="4" t="n">
         <v>820</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="1" t="n">
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="4" t="n">
         <v>415.14</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="1" t="n">
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>44243</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="4" t="n">
         <v>1741.47</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="1" t="n">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>44238</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>90111</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="4" t="n">
         <v>-235.65</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="1" t="n">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="4" t="n">
         <v>-717.99</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="1" t="n">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2" t="n">
         <v>44238</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <v>80092</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="4" t="n">
         <v>-674.5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="1" t="n">
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="2" t="n">
         <v>44238</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="1" t="n">
         <v>80093</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="4" t="n">
         <v>-1985.98</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="1" t="n">
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="2" t="n">
         <v>44229</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="4" t="n">
         <v>-920.56</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="1" t="n">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2" t="n">
         <v>44244</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="1" t="n">
         <v>80096</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="4" t="n">
         <v>-6105.55</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="1" t="n">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="2" t="n">
         <v>44243</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="4" t="n">
         <v>4364.52</v>
       </c>
     </row>
